--- a/artfynd/A 14956-2025 artfynd.xlsx
+++ b/artfynd/A 14956-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>126841835</v>
       </c>
       <c r="B3" t="n">
-        <v>98339</v>
+        <v>98414</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14956-2025 artfynd.xlsx
+++ b/artfynd/A 14956-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>126841835</v>
       </c>
       <c r="B3" t="n">
-        <v>98414</v>
+        <v>98420</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14956-2025 artfynd.xlsx
+++ b/artfynd/A 14956-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>126841835</v>
       </c>
       <c r="B3" t="n">
-        <v>98420</v>
+        <v>98421</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14956-2025 artfynd.xlsx
+++ b/artfynd/A 14956-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>126841835</v>
       </c>
       <c r="B3" t="n">
-        <v>98421</v>
+        <v>98425</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14956-2025 artfynd.xlsx
+++ b/artfynd/A 14956-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>126841835</v>
       </c>
       <c r="B3" t="n">
-        <v>98425</v>
+        <v>98426</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14956-2025 artfynd.xlsx
+++ b/artfynd/A 14956-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>126841835</v>
       </c>
       <c r="B3" t="n">
-        <v>98426</v>
+        <v>98414</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14956-2025 artfynd.xlsx
+++ b/artfynd/A 14956-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111266921</v>
+        <v>126841835</v>
       </c>
       <c r="B2" t="n">
-        <v>103275</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>224098</v>
+        <v>219798</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>skog NV Persberg, Norra Åsta, Nrk</t>
+          <t>Skog NV Persberg, Norra Åsta, Slyte, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529154.0264435894</v>
+        <v>529112</v>
       </c>
       <c r="R2" t="n">
-        <v>6578822.826367664</v>
+        <v>6578467</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126841835</v>
+        <v>111266921</v>
       </c>
       <c r="B3" t="n">
-        <v>98426</v>
+        <v>106231</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219798</v>
+        <v>224098</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skog NV Persberg, Norra Åsta, Slyte, Nrk</t>
+          <t>skog NV Persberg, Norra Åsta, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529112</v>
+        <v>529154</v>
       </c>
       <c r="R3" t="n">
-        <v>6578467</v>
+        <v>6578823</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2023-07-24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2023-07-24</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 14956-2025 artfynd.xlsx
+++ b/artfynd/A 14956-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126841835</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,8 +876,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111266921</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>